--- a/results/monthly_investor_report_2026-10-15.xlsx
+++ b/results/monthly_investor_report_2026-10-15.xlsx
@@ -624,7 +624,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-17 06:19</t>
+          <t>Son Güncelleme: 2026-10-18 06:41</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1115,7 +1115,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-17 06:19</t>
+          <t>Son Güncelleme: 2026-10-18 06:41</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1312,7 +1312,7 @@
         <v>401.5</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>-0.0339316023388089</v>
+        <v>-0.0339316023388087</v>
       </c>
       <c r="F8" s="15" t="n">
         <v>0.0190289400950367</v>
@@ -1321,7 +1321,7 @@
         <v>0.0722991184716234</v>
       </c>
       <c r="H8" s="14" t="n">
-        <v>387.8764616609682</v>
+        <v>387.8764616609683</v>
       </c>
       <c r="I8" s="14" t="n">
         <v>409.1401194481572</v>
@@ -1684,7 +1684,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-17 06:19</t>
+          <t>Son Güncelleme: 2026-10-18 06:41</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1781,7 +1781,7 @@
         <v>0.009822246565652301</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>0.09148572652625959</v>
+        <v>0.0914857265262594</v>
       </c>
       <c r="H4" s="15" t="n">
         <v>-0.08444800886198769</v>
@@ -1818,13 +1818,13 @@
         </is>
       </c>
       <c r="E5" s="15" t="n">
-        <v>0.0213074764962923</v>
+        <v>0.0213074764962926</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>0.0555555088848078</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0.0333169406644697</v>
+        <v>0.0333169406644699</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>-0.123075695465797</v>
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="J5" s="15" t="n">
-        <v>0.0208420951766543</v>
+        <v>0.0208420951766542</v>
       </c>
       <c r="K5" s="15" t="n">
         <v>0.0185279533884517</v>
@@ -1864,7 +1864,7 @@
         <v>0.1075268172583339</v>
       </c>
       <c r="F6" s="18" t="n">
-        <v>0.0772324264604336</v>
+        <v>0.0772324264604338</v>
       </c>
       <c r="G6" s="18" t="n">
         <v>-0.0346070883732535</v>
@@ -1993,7 +1993,7 @@
         <v>0.0753307314128375</v>
       </c>
       <c r="F9" s="20" t="n">
-        <v>-0.142201769844607</v>
+        <v>-0.1422017698446069</v>
       </c>
       <c r="G9" s="20" t="n">
         <v>0.1846415657271476</v>
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="J12" s="20" t="n">
-        <v>0.0179810570574388</v>
+        <v>0.0179810570574387</v>
       </c>
       <c r="K12" s="20" t="n">
         <v>0.0696037442997602</v>
@@ -2182,7 +2182,7 @@
         <v>0.021348496351713</v>
       </c>
       <c r="K13" s="20" t="n">
-        <v>0.0406249908410989</v>
+        <v>0.0406249908410991</v>
       </c>
     </row>
     <row r="14">
@@ -2211,7 +2211,7 @@
         <v>-0.1072080306896575</v>
       </c>
       <c r="G14" s="22" t="n">
-        <v>-0.1542782968447803</v>
+        <v>-0.1542782968447804</v>
       </c>
       <c r="H14" s="22" t="n">
         <v>-0.3546968211243853</v>
@@ -2222,7 +2222,7 @@
         </is>
       </c>
       <c r="J14" s="22" t="n">
-        <v>0.0202170048918636</v>
+        <v>0.0202170048918635</v>
       </c>
       <c r="K14" s="22" t="n">
         <v>0.0124596506797498</v>
@@ -2251,10 +2251,10 @@
         <v>-0.1185952285932669</v>
       </c>
       <c r="F15" s="24" t="n">
-        <v>-0.2224478880176887</v>
+        <v>-0.2224478880176889</v>
       </c>
       <c r="G15" s="24" t="n">
-        <v>-0.3578019713792729</v>
+        <v>-0.357801971379273</v>
       </c>
       <c r="H15" s="24" t="n">
         <v>-0.0237804713987</v>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="J15" s="24" t="n">
-        <v>0.0153242689052913</v>
+        <v>0.0153242689052914</v>
       </c>
       <c r="K15" s="24" t="n">
         <v>-0.0169388433571329</v>
@@ -2308,7 +2308,7 @@
         </is>
       </c>
       <c r="J16" s="22" t="n">
-        <v>0.0184647467983716</v>
+        <v>0.0184647467983715</v>
       </c>
       <c r="K16" s="22" t="n">
         <v>0</v>
@@ -2516,7 +2516,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-17 06:19</t>
+          <t>Son Güncelleme: 2026-10-18 06:41</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2635,7 +2635,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-17 06:19</t>
+          <t>Son Güncelleme: 2026-10-18 06:41</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2886,7 +2886,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-17 06:19</t>
+          <t>Son Güncelleme: 2026-10-18 06:41</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2990,7 +2990,7 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -3011,7 +3011,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-17 06:19</t>
+          <t>Son Güncelleme: 2026-10-18 06:41</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3082,13 +3082,13 @@
         <v>210.8999938964844</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>0.0705583446522049</v>
+        <v>0.07055834465220512</v>
       </c>
       <c r="F4" s="25" t="n">
-        <v>205066.873825042</v>
+        <v>205066.8738250425</v>
       </c>
       <c r="G4" s="25" t="n">
-        <v>19842918.11965895</v>
+        <v>24703770.6565244</v>
       </c>
       <c r="H4" s="26" t="n">
         <v>-0.1192206512468987</v>
@@ -3118,7 +3118,7 @@
         <v>-10146.44124932901</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>19842918.11965895</v>
+        <v>24703770.6565244</v>
       </c>
       <c r="H5" s="26" t="n">
         <v>-0.1192206512468987</v>
@@ -3148,7 +3148,7 @@
         <v>-27972.56036592275</v>
       </c>
       <c r="G6" s="25" t="n">
-        <v>19842918.11965895</v>
+        <v>24703770.6565244</v>
       </c>
       <c r="H6" s="26" t="n">
         <v>-0.1192206512468987</v>
@@ -3178,7 +3178,7 @@
         <v>-384659.1948204595</v>
       </c>
       <c r="G7" s="25" t="n">
-        <v>19842918.11965895</v>
+        <v>24703770.6565244</v>
       </c>
       <c r="H7" s="26" t="n">
         <v>-0.1192206512468987</v>
@@ -3208,7 +3208,7 @@
         <v>-27894.48093186226</v>
       </c>
       <c r="G8" s="25" t="n">
-        <v>19842918.11965895</v>
+        <v>24703770.6565244</v>
       </c>
       <c r="H8" s="26" t="n">
         <v>-0.1192206512468987</v>

--- a/results/monthly_investor_report_2026-10-15.xlsx
+++ b/results/monthly_investor_report_2026-10-15.xlsx
@@ -624,7 +624,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-18 06:41</t>
+          <t>Son Güncelleme: 2026-10-19 07:02</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1115,7 +1115,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-18 06:41</t>
+          <t>Son Güncelleme: 2026-10-19 07:02</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1684,7 +1684,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-18 06:41</t>
+          <t>Son Güncelleme: 2026-10-19 07:02</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2516,7 +2516,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-18 06:41</t>
+          <t>Son Güncelleme: 2026-10-19 07:02</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2635,7 +2635,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-18 06:41</t>
+          <t>Son Güncelleme: 2026-10-19 07:02</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2886,7 +2886,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-18 06:41</t>
+          <t>Son Güncelleme: 2026-10-19 07:02</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2990,7 +2990,7 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -3011,7 +3011,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-18 06:41</t>
+          <t>Son Güncelleme: 2026-10-19 07:02</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3088,7 +3088,7 @@
         <v>205066.8738250425</v>
       </c>
       <c r="G4" s="25" t="n">
-        <v>24703770.6565244</v>
+        <v>29564623.19338985</v>
       </c>
       <c r="H4" s="26" t="n">
         <v>-0.1192206512468987</v>
@@ -3118,7 +3118,7 @@
         <v>-10146.44124932901</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>24703770.6565244</v>
+        <v>29564623.19338985</v>
       </c>
       <c r="H5" s="26" t="n">
         <v>-0.1192206512468987</v>
@@ -3148,7 +3148,7 @@
         <v>-27972.56036592275</v>
       </c>
       <c r="G6" s="25" t="n">
-        <v>24703770.6565244</v>
+        <v>29564623.19338985</v>
       </c>
       <c r="H6" s="26" t="n">
         <v>-0.1192206512468987</v>
@@ -3178,7 +3178,7 @@
         <v>-384659.1948204595</v>
       </c>
       <c r="G7" s="25" t="n">
-        <v>24703770.6565244</v>
+        <v>29564623.19338985</v>
       </c>
       <c r="H7" s="26" t="n">
         <v>-0.1192206512468987</v>
@@ -3208,7 +3208,7 @@
         <v>-27894.48093186226</v>
       </c>
       <c r="G8" s="25" t="n">
-        <v>24703770.6565244</v>
+        <v>29564623.19338985</v>
       </c>
       <c r="H8" s="26" t="n">
         <v>-0.1192206512468987</v>
